--- a/new original/_Dialog/dialog.xlsx
+++ b/new original/_Dialog/dialog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="509">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -315,6 +315,15 @@
   </si>
   <si>
     <t xml:space="preserve">tail3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tail4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">どうした{のだ}、#pc？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why are you looking at me, #pc?</t>
   </si>
   <si>
     <t xml:space="preserve">lockpick_purse</t>
@@ -737,6 +746,51 @@
   </si>
   <si>
     <t xml:space="preserve">...Do you recall when I told you, 'Don't lose it'? Here’s another, so take care of it this time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">はい…喜んで。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes...with pleasure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_deed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}。でも、挙式許可証が必要な{のだ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That makes me happy. But we need a Wedding Permit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}。でも、拠点でゆっくり話そう{よ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That makes me happy. But let's take our time and talk at home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本当に？（現在のパーティーは解散され、#tgと二人きりのパーティーが編成される）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are you serious? (Your current party is disbanded, and a new party is formed with just you and #tg.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_accept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嬉しい{よ}、#pc！ 私はとても幸せ{だ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm so happy, #pc! I'm truly happy.</t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -1133,6 +1187,57 @@
 How may I serve you today?</t>
   </si>
   <si>
+    <t xml:space="preserve">bottle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リュシア|帰らぬ船|この瓶が誰かの手に届くなら、私はもう海の底でしょう。けれど空はとても青かった。
+名もなき兵士|最後の手紙|剣より重いのは恐怖だった。それでも私は逃げなかったと、誰かに知ってほしい。
+エルネス|潮騒の祈り|神よ、波を鎮める力がないなら、せめて眠りをください。
+ミレイユ|約束の浜辺|先に着いたら火を焚いて待っているわ。迷わず来て。
+航海士ダロス|星の記録|星は今日も正しかった。間違えたのは私だ。
+セレナ|ささやかな告白|あなたの名前を声に出せなかった。それだけが心残りです。
+老人|若き日へ|海は奪うが、すべてを無駄にはしない。生き延びろ。
+双子の妹|半分の世界|兄さん、世界はまだ半分残っているよ。だから帰ってきて。
+船医レナート|診療記録|傷は治せなかったが、痛みは和らげられた。それで十分だ。
+イザベル|歌の続きを|私がいなくても、この歌を最後まで歌って。
+密輸人カイル|報酬の行方|金は北の入り江に沈めた。欲しければ潜れ。
+神官見習いロア|疑いの告白|祈りは届かなかった。それでも私は祈ることをやめない。
+漁師ハルド|最後の漁|今日の獲物はなかった。でも海と話はできた。
+旅人シアン|通過点|ここは終わりじゃない。ただの通過点だ。
+王国書記官|公式記録抄|本船は嵐により喪失。以上。
+母|子へ|寒くなったら外套を着なさい。約束よ。
+吟遊詩人フェイ|未完成の詩|韻が足りない。続きを考えてくれる人へ。
+傭兵団長ヴォルク|撤退命令|生きて帰れ。名誉は後で拾えばいい。
+少女|はじめての旅|少し怖い。でも楽しい。
+誰か|拾ったあなたへ|あなたがこれを読んでいるなら、世界はまだ続いている。
+不明|お…|おうち…かえう…！
+不明|もう…|もうだめぽ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucia|The Ship That Never Returned|If this bottle reaches someone,I will likely be beneath the sea by then.But the sky was very blue.
+An Unnamed Soldier|Final Letter|Fear weighed heavier than my sword.But I want someone to know I did not run.
+Ernes|Prayer of the Surf|God,if you cannot calm the waves,then at least grant me sleep.
+Mireille|The Promised Shore|If I arrive first,I will light a fire and wait.Come without losing your way.
+Navigator Daros|Record of the Stars|The stars were correct again today.The one who erred was me.
+Selena|A Small Confession|I could never speak your name aloud.That is my only regret.
+Old Man|To My Younger Days|The sea takes much,but nothing is entirely wasted.Survive.
+The Younger Twin|Half the World Left|Brother,half the world is still here.So please come back.
+Ship Doctor Renato|Medical Notes|I could not heal the wounds,but I eased the pain.That was enough.
+Isabelle|Finish the Song|Even if I am gone,please sing this song to the end.
+Smuggler Kyle|Where the Payment Lies|The gold is sunk in the northern cove.Dive if you want it.
+Acolyte Roa|Confession of Doubt|My prayers were unanswered.Still,I will not stop praying.
+Fisherman Hald|The Last Catch|There was no catch today.But I spoke with the sea.
+Traveler Cyan|A Passing Point|This is not the end.It is only a passing point.
+Royal Scribe|Excerpt from Official Records|The vessel was lost to the storm.End of report.
+Mother|To My Child|Put on your cloak when it gets cold.Promise me.
+Bard Fey|An Unfinished Poem|The rhyme is missing.To whoever finishes it.
+Mercenary Captain Volk|Order to Retreat|Come back alive.Honor can be picked up later.
+Little Girl|My First Journey|I'm a little scared.But it's fun.
+Someone|To Whoever Finds This|If you are reading this,the world is still going on.
+Unknown|I...|I'm...going...home...!
+Unknown|I'm...|Moudamepo</t>
+  </si>
+  <si>
     <t xml:space="preserve">mysilia</t>
   </si>
   <si>
@@ -1417,6 +1522,23 @@
 Our great father oversees our penance, and there is no escape from our fates.
 As time passes, we grow less concerned with our material conditions...
 Yes #race, you're standing in front of an exile who has lived more than 1000 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mimu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">……ぴ？
+…………ぴぴ
+ピ………
+…ピぽ………
+……ぴ……エラー……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…Pi?
+……Pipi
+Pi………
+…Pipo………
+……Pi……Error……</t>
   </si>
   <si>
     <t xml:space="preserve">namamani</t>
@@ -3012,9 +3134,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>278280</xdr:colOff>
+      <xdr:colOff>275760</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>117000</xdr:rowOff>
+      <xdr:rowOff>114480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3024,7 +3146,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49657680" cy="117000"/>
+          <a:ext cx="49655160" cy="114480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3162,7 +3284,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.11"/>
@@ -3600,7 +3722,7 @@
       <c r="A42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -3680,22 +3802,22 @@
       <c r="C49" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>138</v>
       </c>
@@ -3728,7 +3850,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
@@ -3750,7 +3872,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>153</v>
       </c>
@@ -3761,7 +3883,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>156</v>
       </c>
@@ -3790,7 +3912,7 @@
       <c r="C59" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="1" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3801,7 +3923,7 @@
       <c r="C60" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="4" t="s">
         <v>167</v>
       </c>
     </row>
@@ -3823,7 +3945,7 @@
       <c r="C62" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3834,7 +3956,7 @@
       <c r="C63" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="3" t="s">
         <v>176</v>
       </c>
     </row>
@@ -3845,7 +3967,7 @@
       <c r="C64" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="4" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3889,12 +4011,12 @@
       <c r="C68" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="1" t="s">
         <v>192</v>
       </c>
       <c r="C69" s="3" t="s">
@@ -3904,8 +4026,8 @@
         <v>194</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C70" s="3" t="s">
@@ -3926,14 +4048,14 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="3" t="s">
         <v>203</v>
       </c>
     </row>
@@ -3952,10 +4074,10 @@
       <c r="A74" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="1" t="s">
         <v>209</v>
       </c>
     </row>
@@ -3974,7 +4096,7 @@
       <c r="A76" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -3992,18 +4114,18 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>222</v>
       </c>
@@ -4018,7 +4140,7 @@
       <c r="A80" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="3" t="s">
         <v>226</v>
       </c>
       <c r="D80" s="4" t="s">
@@ -4045,6 +4167,72 @@
       </c>
       <c r="D82" s="4" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4064,7 +4252,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="13.63"/>
@@ -4098,213 +4286,224 @@
     </row>
     <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="200.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>290</v>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4348,149 +4547,149 @@
     </row>
     <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="3" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="3" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="3" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4509,7 +4708,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.58"/>
@@ -4541,494 +4740,505 @@
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>336</v>
+        <v>355</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>339</v>
+        <v>358</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>360</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B18" s="3"/>
+        <v>390</v>
+      </c>
       <c r="C18" s="3" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>372</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>394</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>397</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>418</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>421</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>423</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
-        <v>408</v>
+        <v>426</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>432</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="B35" s="5"/>
+        <v>434</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>440</v>
+      </c>
       <c r="C35" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>441</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="3" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="3" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B38" s="5"/>
-      <c r="C38" s="5" t="s">
-        <v>429</v>
+      <c r="C38" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="3" t="s">
-        <v>432</v>
+      <c r="C39" s="5" t="s">
+        <v>453</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>434</v>
-      </c>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B40" s="5"/>
       <c r="C40" s="3" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
-        <v>440</v>
+      <c r="A42" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>458</v>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>460</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -5081,90 +5291,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/new original/_Dialog/dialog.xlsx
+++ b/new original/_Dialog/dialog.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="524">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -791,6 +791,87 @@
   </si>
   <si>
     <t xml:space="preserve">I'm so happy, #pc! I'm truly happy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rob1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">見損なった{よ}！
+ひどい{よ}、やめて{くれ}！
+返り討ちにしてくれる{よ}。
+ごろつき風情に何ができるという{のだ}？
+やめて{くれ}。きっと後悔する{よ}。
+傭兵さんたち、このごろつきを追い払って{くれ}。
+ふん、この護衛の数が見えないの{か}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I misjudged you!
+Please, stop this!
+You'll regret coming after me.
+What makes you think a common thug can take me on?
+Please stop. You'll regret this.
+Mercenaries, drive this ruffian off.
+Hmph. Can't you see how many guards I have?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mama_yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ママだよ！
+{はい}、ママ{だ}～！
+ママはここにいる{のだ}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mommy's here!
+Yes, I'm your mommy!
+Mommy is right here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mama_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シッシッ！
+ママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+気持ち悪い{よ}…
+え…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoo, shoo!
+I'm not your mom!
+What are you talking about...?
+How pitiful... did you hit your head?
+That’s creepy...
+Huh...? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">baby_yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ママー！
+私の…ママなの{か}？
+マ…ママ…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mommy!
+...You are my...mommy?
+Ma... mama...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baby_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">こんなのママじゃない{よ}！
+君は何を言っている{のだ}？
+かわいそうに…頭を打ったの{か}？
+え…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You're not my mommy!
+What are you talking about...?
+How pitiful... did you hit your head?
+Huh...? </t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -3134,9 +3215,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>275760</xdr:colOff>
+      <xdr:colOff>274320</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>114480</xdr:rowOff>
+      <xdr:rowOff>113040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3146,7 +3227,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49655160" cy="114480"/>
+          <a:ext cx="49653720" cy="113040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3284,7 +3365,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.11"/>
@@ -4233,6 +4314,61 @@
       </c>
       <c r="D88" s="4" t="s">
         <v>251</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4286,224 +4422,224 @@
     </row>
     <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="200.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -4547,149 +4683,149 @@
     </row>
     <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="3" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="3" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="3" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -4742,308 +4878,308 @@
     </row>
     <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>206</v>
@@ -5051,194 +5187,194 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="3" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="3" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="3" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="3" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -5291,90 +5427,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/new original/_Dialog/dialog.xlsx
+++ b/new original/_Dialog/dialog.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="509">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -791,87 +791,6 @@
   </si>
   <si>
     <t xml:space="preserve">I'm so happy, #pc! I'm truly happy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rob1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">見損なった{よ}！
-ひどい{よ}、やめて{くれ}！
-返り討ちにしてくれる{よ}。
-ごろつき風情に何ができるという{のだ}？
-やめて{くれ}。きっと後悔する{よ}。
-傭兵さんたち、このごろつきを追い払って{くれ}。
-ふん、この護衛の数が見えないの{か}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I misjudged you!
-Please, stop this!
-You'll regret coming after me.
-What makes you think a common thug can take me on?
-Please stop. You'll regret this.
-Mercenaries, drive this ruffian off.
-Hmph. Can't you see how many guards I have?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mama_yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ママだよ！
-{はい}、ママ{だ}～！
-ママはここにいる{のだ}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mommy's here!
-Yes, I'm your mommy!
-Mommy is right here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mama_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シッシッ！
-ママじゃない{よ}！
-君は何を言っている{のだ}？
-かわいそうに…頭を打ったの{か}？
-気持ち悪い{よ}…
-え…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoo, shoo!
-I'm not your mom!
-What are you talking about...?
-How pitiful... did you hit your head?
-That’s creepy...
-Huh...? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">baby_yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ママー！
-私の…ママなの{か}？
-マ…ママ…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mommy!
-...You are my...mommy?
-Ma... mama...?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baby_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">こんなのママじゃない{よ}！
-君は何を言っている{のだ}？
-かわいそうに…頭を打ったの{か}？
-え…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You're not my mommy!
-What are you talking about...?
-How pitiful... did you hit your head?
-Huh...? </t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -3215,9 +3134,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:colOff>275760</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
+      <xdr:rowOff>114480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3227,7 +3146,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="49653720" cy="113040"/>
+          <a:ext cx="49655160" cy="114480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3365,7 +3284,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultColWidth="14.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.11"/>
@@ -4314,61 +4233,6 @@
       </c>
       <c r="D88" s="4" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4422,224 +4286,224 @@
     </row>
     <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="200.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4683,149 +4547,149 @@
     </row>
     <row r="5" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="3" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="3" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="3" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="3" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4878,308 +4742,308 @@
     </row>
     <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="79.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>206</v>
@@ -5187,194 +5051,194 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="3" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="3" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="3" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="3" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -5427,90 +5291,90 @@
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="168.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="112.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
